--- a/Structure_Data/text.9.14/20260914_57/structure_factor_20260914_57.xlsx
+++ b/Structure_Data/text.9.14/20260914_57/structure_factor_20260914_57.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D373"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,3939 @@
         <v>19.6664110562933</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.233562469482422</v>
+      </c>
+      <c r="C30">
+        <v>0.232704162597656</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.233562469482422</v>
+      </c>
+      <c r="C31">
+        <v>0.232704162597656</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.163356781005859</v>
+      </c>
+      <c r="C32">
+        <v>0.00885772705078125</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.072357177734375</v>
+      </c>
+      <c r="C33">
+        <v>0.00187301635742188</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.0449447631835938</v>
+      </c>
+      <c r="C34">
+        <v>0.000110626220703125</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B35">
+        <v>0.0269126892089844</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B36">
+        <v>0.00640869140625</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B37">
+        <v>0.0023345947265625</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1.5</v>
+      </c>
+      <c r="B38">
+        <v>0.000640869140625</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>2</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>20677</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>1.48055810804275</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>1.22588326678781</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.05</v>
+      </c>
+      <c r="B55">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.1</v>
+      </c>
+      <c r="B56">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.15</v>
+      </c>
+      <c r="B57">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.2</v>
+      </c>
+      <c r="B58">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.25</v>
+      </c>
+      <c r="B59">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.3</v>
+      </c>
+      <c r="B60">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.35</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.4</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.45</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.5</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.55</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.6</v>
+      </c>
+      <c r="B66">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.7</v>
+      </c>
+      <c r="B68">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.75</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.8</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.85</v>
+      </c>
+      <c r="B71">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.9</v>
+      </c>
+      <c r="B72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.95</v>
+      </c>
+      <c r="B73">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.5</v>
+      </c>
+      <c r="B75">
+        <v>7045</v>
+      </c>
+      <c r="C75">
+        <v>0.340716738404991</v>
+      </c>
+      <c r="D75">
+        <v>0.340716738404991</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>1</v>
+      </c>
+      <c r="B76">
+        <v>4693</v>
+      </c>
+      <c r="C76">
+        <v>0.2269671615805</v>
+      </c>
+      <c r="D76">
+        <v>0.567683899985491</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>1.5</v>
+      </c>
+      <c r="B77">
+        <v>3026</v>
+      </c>
+      <c r="C77">
+        <v>0.146346181747836</v>
+      </c>
+      <c r="D77">
+        <v>0.714030081733327</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>2</v>
+      </c>
+      <c r="B78">
+        <v>1963</v>
+      </c>
+      <c r="C78">
+        <v>0.0949364027663588</v>
+      </c>
+      <c r="D78">
+        <v>0.808966484499686</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>2.5</v>
+      </c>
+      <c r="B79">
+        <v>1273</v>
+      </c>
+      <c r="C79">
+        <v>0.0615659911979494</v>
+      </c>
+      <c r="D79">
+        <v>0.870532475697635</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>3</v>
+      </c>
+      <c r="B80">
+        <v>912</v>
+      </c>
+      <c r="C80">
+        <v>0.0441069787686802</v>
+      </c>
+      <c r="D80">
+        <v>0.914639454466315</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>3.5</v>
+      </c>
+      <c r="B81">
+        <v>573</v>
+      </c>
+      <c r="C81">
+        <v>0.0277119504763747</v>
+      </c>
+      <c r="D81">
+        <v>0.94235140494269</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>4</v>
+      </c>
+      <c r="B82">
+        <v>386</v>
+      </c>
+      <c r="C82">
+        <v>0.0186680853121826</v>
+      </c>
+      <c r="D82">
+        <v>0.961019490254873</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>4.5</v>
+      </c>
+      <c r="B83">
+        <v>248</v>
+      </c>
+      <c r="C83">
+        <v>0.0119940029985007</v>
+      </c>
+      <c r="D83">
+        <v>0.973013493253373</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>5</v>
+      </c>
+      <c r="B84">
+        <v>186</v>
+      </c>
+      <c r="C84">
+        <v>0.00899550224887556</v>
+      </c>
+      <c r="D84">
+        <v>0.982008995502249</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>5.5</v>
+      </c>
+      <c r="B85">
+        <v>114</v>
+      </c>
+      <c r="C85">
+        <v>0.00551337234608502</v>
+      </c>
+      <c r="D85">
+        <v>0.987522367848334</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>6</v>
+      </c>
+      <c r="B86">
+        <v>88</v>
+      </c>
+      <c r="C86">
+        <v>0.00425593654785511</v>
+      </c>
+      <c r="D86">
+        <v>0.991778304396189</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>6.5</v>
+      </c>
+      <c r="B87">
+        <v>60</v>
+      </c>
+      <c r="C87">
+        <v>0.00290177491899212</v>
+      </c>
+      <c r="D87">
+        <v>0.994680079315181</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>7</v>
+      </c>
+      <c r="B88">
+        <v>36</v>
+      </c>
+      <c r="C88">
+        <v>0.00174106495139527</v>
+      </c>
+      <c r="D88">
+        <v>0.996421144266576</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>7.5</v>
+      </c>
+      <c r="B89">
+        <v>24</v>
+      </c>
+      <c r="C89">
+        <v>0.00116070996759685</v>
+      </c>
+      <c r="D89">
+        <v>0.997581854234173</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>8</v>
+      </c>
+      <c r="B90">
+        <v>23</v>
+      </c>
+      <c r="C90">
+        <v>0.00111234705228031</v>
+      </c>
+      <c r="D90">
+        <v>0.998694201286454</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>8.5</v>
+      </c>
+      <c r="B91">
+        <v>8</v>
+      </c>
+      <c r="C91">
+        <v>0.000386903322532282</v>
+      </c>
+      <c r="D91">
+        <v>0.999081104608986</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>9</v>
+      </c>
+      <c r="B92">
+        <v>7</v>
+      </c>
+      <c r="C92">
+        <v>0.000338540407215747</v>
+      </c>
+      <c r="D92">
+        <v>0.999419645016202</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>9.5</v>
+      </c>
+      <c r="B93">
+        <v>3</v>
+      </c>
+      <c r="C93">
+        <v>0.000145088745949606</v>
+      </c>
+      <c r="D93">
+        <v>0.999564733762151</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>10</v>
+      </c>
+      <c r="B94">
+        <v>4</v>
+      </c>
+      <c r="C94">
+        <v>0.000193451661266141</v>
+      </c>
+      <c r="D94">
+        <v>0.999758185423417</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>10.5</v>
+      </c>
+      <c r="B95">
+        <v>2</v>
+      </c>
+      <c r="C95">
+        <v>9.67258306330706e-05</v>
+      </c>
+      <c r="D95">
+        <v>0.99985491125405</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>11</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96">
+        <v>4.83629153165353e-05</v>
+      </c>
+      <c r="D96">
+        <v>0.999903274169367</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>11.5</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97">
+        <v>4.83629153165353e-05</v>
+      </c>
+      <c r="D97">
+        <v>0.999951637084683</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>15</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98">
+        <v>4.83629153165353e-05</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99"/>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>200917</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>0.885300146858817</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>0.475059603468639</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>0.05</v>
+      </c>
+      <c r="B113">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>0.1</v>
+      </c>
+      <c r="B114">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>0.15</v>
+      </c>
+      <c r="B115">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>0.2</v>
+      </c>
+      <c r="B116">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>0.25</v>
+      </c>
+      <c r="B117">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>0.3</v>
+      </c>
+      <c r="B118">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>0.35</v>
+      </c>
+      <c r="B119">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>0.4</v>
+      </c>
+      <c r="B120">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>0.45</v>
+      </c>
+      <c r="B121">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>0.5</v>
+      </c>
+      <c r="B122">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>0.55</v>
+      </c>
+      <c r="B123">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>0.6</v>
+      </c>
+      <c r="B124">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>0.65</v>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>0.7</v>
+      </c>
+      <c r="B126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>0.75</v>
+      </c>
+      <c r="B127">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>0.8</v>
+      </c>
+      <c r="B128">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>0.85</v>
+      </c>
+      <c r="B129">
+        <v>1.22474487139159</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>0.9</v>
+      </c>
+      <c r="B130">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>0.95</v>
+      </c>
+      <c r="B131">
+        <v>1.73205080756888</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>0.5</v>
+      </c>
+      <c r="B133">
+        <v>70384</v>
+      </c>
+      <c r="C133">
+        <v>0.350313811175759</v>
+      </c>
+      <c r="D133">
+        <v>0.350313811175759</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B134">
+        <v>41272</v>
+      </c>
+      <c r="C134">
+        <v>0.205418157746731</v>
+      </c>
+      <c r="D134">
+        <v>0.55573196892249</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B135">
+        <v>17038</v>
+      </c>
+      <c r="C135">
+        <v>0.0848011865596241</v>
+      </c>
+      <c r="D135">
+        <v>0.640533155482115</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>1</v>
+      </c>
+      <c r="B136">
+        <v>13616</v>
+      </c>
+      <c r="C136">
+        <v>0.0677692778610073</v>
+      </c>
+      <c r="D136">
+        <v>0.708302433343122</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B137">
+        <v>23051</v>
+      </c>
+      <c r="C137">
+        <v>0.114728967683173</v>
+      </c>
+      <c r="D137">
+        <v>0.823031401026294</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B138">
+        <v>9241</v>
+      </c>
+      <c r="C138">
+        <v>0.0459941169736757</v>
+      </c>
+      <c r="D138">
+        <v>0.86902551799997</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B139">
+        <v>6039</v>
+      </c>
+      <c r="C139">
+        <v>0.0300571877939647</v>
+      </c>
+      <c r="D139">
+        <v>0.899082705793935</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>1.5</v>
+      </c>
+      <c r="B140">
+        <v>6121</v>
+      </c>
+      <c r="C140">
+        <v>0.0304653165237387</v>
+      </c>
+      <c r="D140">
+        <v>0.929548022317673</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B141">
+        <v>2399</v>
+      </c>
+      <c r="C141">
+        <v>0.0119402539357048</v>
+      </c>
+      <c r="D141">
+        <v>0.941488276253378</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B142">
+        <v>1569</v>
+      </c>
+      <c r="C142">
+        <v>0.00780919484165103</v>
+      </c>
+      <c r="D142">
+        <v>0.949297471095029</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B143">
+        <v>554</v>
+      </c>
+      <c r="C143">
+        <v>0.0027573575157901</v>
+      </c>
+      <c r="D143">
+        <v>0.952054828610819</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B144">
+        <v>1205</v>
+      </c>
+      <c r="C144">
+        <v>0.00599750145582504</v>
+      </c>
+      <c r="D144">
+        <v>0.958052330066644</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B145">
+        <v>1323</v>
+      </c>
+      <c r="C145">
+        <v>0.00658480865232907</v>
+      </c>
+      <c r="D145">
+        <v>0.964637138718973</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>2</v>
+      </c>
+      <c r="B146">
+        <v>364</v>
+      </c>
+      <c r="C146">
+        <v>0.00181169338582599</v>
+      </c>
+      <c r="D146">
+        <v>0.966448832104799</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B147">
+        <v>1039</v>
+      </c>
+      <c r="C147">
+        <v>0.00517128963701429</v>
+      </c>
+      <c r="D147">
+        <v>0.971620121741814</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B148">
+        <v>565</v>
+      </c>
+      <c r="C148">
+        <v>0.00281210649173539</v>
+      </c>
+      <c r="D148">
+        <v>0.974432228233549</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B149">
+        <v>308</v>
+      </c>
+      <c r="C149">
+        <v>0.00153297132646814</v>
+      </c>
+      <c r="D149">
+        <v>0.975965199560017</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B150">
+        <v>314</v>
+      </c>
+      <c r="C150">
+        <v>0.00156283440425648</v>
+      </c>
+      <c r="D150">
+        <v>0.977528033964274</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B151">
+        <v>480</v>
+      </c>
+      <c r="C151">
+        <v>0.00238904622306724</v>
+      </c>
+      <c r="D151">
+        <v>0.979917080187341</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B152">
+        <v>203</v>
+      </c>
+      <c r="C152">
+        <v>0.00101036746517219</v>
+      </c>
+      <c r="D152">
+        <v>0.980927447652513</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B153">
+        <v>198</v>
+      </c>
+      <c r="C153">
+        <v>0.000985481567015235</v>
+      </c>
+      <c r="D153">
+        <v>0.981912929219528</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>2.5</v>
+      </c>
+      <c r="B154">
+        <v>360</v>
+      </c>
+      <c r="C154">
+        <v>0.00179178466730043</v>
+      </c>
+      <c r="D154">
+        <v>0.983704713886829</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B155">
+        <v>508</v>
+      </c>
+      <c r="C155">
+        <v>0.00252840725274616</v>
+      </c>
+      <c r="D155">
+        <v>0.986233121139575</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>2.59807621135332</v>
+      </c>
+      <c r="B156">
+        <v>181</v>
+      </c>
+      <c r="C156">
+        <v>0.000900869513281604</v>
+      </c>
+      <c r="D156">
+        <v>0.987133990652857</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>2.69258240356725</v>
+      </c>
+      <c r="B157">
+        <v>364</v>
+      </c>
+      <c r="C157">
+        <v>0.00181169338582599</v>
+      </c>
+      <c r="D157">
+        <v>0.988945684038683</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>2.73861278752583</v>
+      </c>
+      <c r="B158">
+        <v>206</v>
+      </c>
+      <c r="C158">
+        <v>0.00102529900406636</v>
+      </c>
+      <c r="D158">
+        <v>0.989970983042749</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>2.82842712474619</v>
+      </c>
+      <c r="B159">
+        <v>58</v>
+      </c>
+      <c r="C159">
+        <v>0.000288676418620624</v>
+      </c>
+      <c r="D159">
+        <v>0.99025965946137</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>2.87228132326901</v>
+      </c>
+      <c r="B160">
+        <v>186</v>
+      </c>
+      <c r="C160">
+        <v>0.000925755411438554</v>
+      </c>
+      <c r="D160">
+        <v>0.991185414872808</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>2.91547594742265</v>
+      </c>
+      <c r="B161">
+        <v>167</v>
+      </c>
+      <c r="C161">
+        <v>0.000831188998442143</v>
+      </c>
+      <c r="D161">
+        <v>0.99201660387125</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>2.95803989154981</v>
+      </c>
+      <c r="B162">
+        <v>152</v>
+      </c>
+      <c r="C162">
+        <v>0.000756531303971292</v>
+      </c>
+      <c r="D162">
+        <v>0.992773135175222</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>3</v>
+      </c>
+      <c r="B163">
+        <v>111</v>
+      </c>
+      <c r="C163">
+        <v>0.000552466939084299</v>
+      </c>
+      <c r="D163">
+        <v>0.993325602114306</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>3.04138126514911</v>
+      </c>
+      <c r="B164">
+        <v>87</v>
+      </c>
+      <c r="C164">
+        <v>0.000433014627930937</v>
+      </c>
+      <c r="D164">
+        <v>0.993758616742237</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>3.08220700148449</v>
+      </c>
+      <c r="B165">
+        <v>164</v>
+      </c>
+      <c r="C165">
+        <v>0.000816257459547973</v>
+      </c>
+      <c r="D165">
+        <v>0.994574874201785</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="B166">
+        <v>69</v>
+      </c>
+      <c r="C166">
+        <v>0.000343425394565915</v>
+      </c>
+      <c r="D166">
+        <v>0.994918299596351</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>3.20156211871642</v>
+      </c>
+      <c r="B167">
+        <v>185</v>
+      </c>
+      <c r="C167">
+        <v>0.000920778231807164</v>
+      </c>
+      <c r="D167">
+        <v>0.995839077828158</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>3.24037034920393</v>
+      </c>
+      <c r="B168">
+        <v>69</v>
+      </c>
+      <c r="C168">
+        <v>0.000343425394565915</v>
+      </c>
+      <c r="D168">
+        <v>0.996182503222724</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>3.278719262151</v>
+      </c>
+      <c r="B169">
+        <v>21</v>
+      </c>
+      <c r="C169">
+        <v>0.000104520772259192</v>
+      </c>
+      <c r="D169">
+        <v>0.996287023994983</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>3.3166247903554</v>
+      </c>
+      <c r="B170">
+        <v>37</v>
+      </c>
+      <c r="C170">
+        <v>0.000184155646361433</v>
+      </c>
+      <c r="D170">
+        <v>0.996471179641344</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>3.35410196624968</v>
+      </c>
+      <c r="B171">
+        <v>86</v>
+      </c>
+      <c r="C171">
+        <v>0.000428037448299547</v>
+      </c>
+      <c r="D171">
+        <v>0.996899217089644</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>3.39116499156263</v>
+      </c>
+      <c r="B172">
+        <v>48</v>
+      </c>
+      <c r="C172">
+        <v>0.000238904622306724</v>
+      </c>
+      <c r="D172">
+        <v>0.997138121711951</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>3.46410161513775</v>
+      </c>
+      <c r="B173">
+        <v>6</v>
+      </c>
+      <c r="C173">
+        <v>2.98630777883405e-05</v>
+      </c>
+      <c r="D173">
+        <v>0.997167984789739</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>3.5</v>
+      </c>
+      <c r="B174">
+        <v>74</v>
+      </c>
+      <c r="C174">
+        <v>0.000368311292722866</v>
+      </c>
+      <c r="D174">
+        <v>0.997536296082462</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>3.53553390593274</v>
+      </c>
+      <c r="B175">
+        <v>62</v>
+      </c>
+      <c r="C175">
+        <v>0.000308585137146185</v>
+      </c>
+      <c r="D175">
+        <v>0.997844881219608</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>3.57071421427143</v>
+      </c>
+      <c r="B176">
+        <v>37</v>
+      </c>
+      <c r="C176">
+        <v>0.000184155646361433</v>
+      </c>
+      <c r="D176">
+        <v>0.99802903686597</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>3.60555127546399</v>
+      </c>
+      <c r="B177">
+        <v>15</v>
+      </c>
+      <c r="C177">
+        <v>7.46576944708511e-05</v>
+      </c>
+      <c r="D177">
+        <v>0.99810369456044</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>3.64005494464026</v>
+      </c>
+      <c r="B178">
+        <v>50</v>
+      </c>
+      <c r="C178">
+        <v>0.000248858981569504</v>
+      </c>
+      <c r="D178">
+        <v>0.99835255354201</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>3.67423461417477</v>
+      </c>
+      <c r="B179">
+        <v>46</v>
+      </c>
+      <c r="C179">
+        <v>0.000228950263043944</v>
+      </c>
+      <c r="D179">
+        <v>0.998581503805054</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>3.74165738677394</v>
+      </c>
+      <c r="B180">
+        <v>18</v>
+      </c>
+      <c r="C180">
+        <v>8.95892333650214e-05</v>
+      </c>
+      <c r="D180">
+        <v>0.998671093038419</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>3.77491721763537</v>
+      </c>
+      <c r="B181">
+        <v>19</v>
+      </c>
+      <c r="C181">
+        <v>9.45664129964115e-05</v>
+      </c>
+      <c r="D181">
+        <v>0.998765659451415</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>3.80788655293195</v>
+      </c>
+      <c r="B182">
+        <v>17</v>
+      </c>
+      <c r="C182">
+        <v>8.46120537336313e-05</v>
+      </c>
+      <c r="D182">
+        <v>0.998850271505149</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>3.8405728739343</v>
+      </c>
+      <c r="B183">
+        <v>24</v>
+      </c>
+      <c r="C183">
+        <v>0.000119452311153362</v>
+      </c>
+      <c r="D183">
+        <v>0.998969723816302</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>3.90512483795333</v>
+      </c>
+      <c r="B184">
+        <v>15</v>
+      </c>
+      <c r="C184">
+        <v>7.46576944708511e-05</v>
+      </c>
+      <c r="D184">
+        <v>0.999044381510773</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>3.93700393700591</v>
+      </c>
+      <c r="B185">
+        <v>36</v>
+      </c>
+      <c r="C185">
+        <v>0.000179178466730043</v>
+      </c>
+      <c r="D185">
+        <v>0.999223559977503</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>4</v>
+      </c>
+      <c r="B186">
+        <v>13</v>
+      </c>
+      <c r="C186">
+        <v>6.4703335208071e-05</v>
+      </c>
+      <c r="D186">
+        <v>0.999288263312711</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>4.03112887414927</v>
+      </c>
+      <c r="B187">
+        <v>30</v>
+      </c>
+      <c r="C187">
+        <v>0.000149315388941702</v>
+      </c>
+      <c r="D187">
+        <v>0.999437578701653</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>4.06201920231798</v>
+      </c>
+      <c r="B188">
+        <v>18</v>
+      </c>
+      <c r="C188">
+        <v>8.95892333650214e-05</v>
+      </c>
+      <c r="D188">
+        <v>0.999527167935018</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>4.09267638593623</v>
+      </c>
+      <c r="B189">
+        <v>7</v>
+      </c>
+      <c r="C189">
+        <v>3.48402574197305e-05</v>
+      </c>
+      <c r="D189">
+        <v>0.999562008192438</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>4.12310562561766</v>
+      </c>
+      <c r="B190">
+        <v>11</v>
+      </c>
+      <c r="C190">
+        <v>5.47489759452908e-05</v>
+      </c>
+      <c r="D190">
+        <v>0.999616757168383</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>4.15331193145904</v>
+      </c>
+      <c r="B191">
+        <v>21</v>
+      </c>
+      <c r="C191">
+        <v>0.000104520772259192</v>
+      </c>
+      <c r="D191">
+        <v>0.999721277940642</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>4.18330013267038</v>
+      </c>
+      <c r="B192">
+        <v>1</v>
+      </c>
+      <c r="C192">
+        <v>4.97717963139008e-06</v>
+      </c>
+      <c r="D192">
+        <v>0.999726255120274</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>4.24264068711928</v>
+      </c>
+      <c r="B193">
+        <v>5</v>
+      </c>
+      <c r="C193">
+        <v>2.48858981569504e-05</v>
+      </c>
+      <c r="D193">
+        <v>0.999751141018431</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>4.27200187265877</v>
+      </c>
+      <c r="B194">
+        <v>8</v>
+      </c>
+      <c r="C194">
+        <v>3.98174370511206e-05</v>
+      </c>
+      <c r="D194">
+        <v>0.999790958455482</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>4.30116263352131</v>
+      </c>
+      <c r="B195">
+        <v>14</v>
+      </c>
+      <c r="C195">
+        <v>6.96805148394611e-05</v>
+      </c>
+      <c r="D195">
+        <v>0.999860638970321</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>4.33012701892219</v>
+      </c>
+      <c r="B196">
+        <v>4</v>
+      </c>
+      <c r="C196">
+        <v>1.99087185255603e-05</v>
+      </c>
+      <c r="D196">
+        <v>0.999880547688847</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>4.38748219369606</v>
+      </c>
+      <c r="B197">
+        <v>6</v>
+      </c>
+      <c r="C197">
+        <v>2.98630777883405e-05</v>
+      </c>
+      <c r="D197">
+        <v>0.999910410766635</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>4.41588043316392</v>
+      </c>
+      <c r="B198">
+        <v>4</v>
+      </c>
+      <c r="C198">
+        <v>1.99087185255603e-05</v>
+      </c>
+      <c r="D198">
+        <v>0.999930319485161</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>4.47213595499958</v>
+      </c>
+      <c r="B199">
+        <v>7</v>
+      </c>
+      <c r="C199">
+        <v>3.48402574197305e-05</v>
+      </c>
+      <c r="D199">
+        <v>0.99996515974258</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>4.5</v>
+      </c>
+      <c r="B200">
+        <v>4</v>
+      </c>
+      <c r="C200">
+        <v>1.99087185255603e-05</v>
+      </c>
+      <c r="D200">
+        <v>0.999985068461106</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>4.55521678957215</v>
+      </c>
+      <c r="B201">
+        <v>1</v>
+      </c>
+      <c r="C201">
+        <v>4.97717963139008e-06</v>
+      </c>
+      <c r="D201">
+        <v>0.999990045640737</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>4.58257569495584</v>
+      </c>
+      <c r="B202">
+        <v>1</v>
+      </c>
+      <c r="C202">
+        <v>4.97717963139008e-06</v>
+      </c>
+      <c r="D202">
+        <v>0.999995022820369</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>4.63680924774785</v>
+      </c>
+      <c r="B203">
+        <v>1</v>
+      </c>
+      <c r="C203">
+        <v>4.97717963139008e-06</v>
+      </c>
+      <c r="D203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204"/>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B209">
+        <v>0.233562469482422</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B210">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>0</v>
+      </c>
+      <c r="B215">
+        <v>0.233562469482422</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+      <c r="D215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>0.5</v>
+      </c>
+      <c r="B216">
+        <v>0.155132293701172</v>
+      </c>
+      <c r="C216">
+        <v>6</v>
+      </c>
+      <c r="D216">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>1</v>
+      </c>
+      <c r="B217">
+        <v>0.121998126690204</v>
+      </c>
+      <c r="C217">
+        <v>26</v>
+      </c>
+      <c r="D217">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>1.5</v>
+      </c>
+      <c r="B218">
+        <v>0.0877905951605903</v>
+      </c>
+      <c r="C218">
+        <v>90</v>
+      </c>
+      <c r="D218">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>2</v>
+      </c>
+      <c r="B219">
+        <v>0.069424757316931</v>
+      </c>
+      <c r="C219">
+        <v>134</v>
+      </c>
+      <c r="D219">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>2.5</v>
+      </c>
+      <c r="B220">
+        <v>0.0597893175228622</v>
+      </c>
+      <c r="C220">
+        <v>258</v>
+      </c>
+      <c r="D220">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>3</v>
+      </c>
+      <c r="B221">
+        <v>0.0568455579804211</v>
+      </c>
+      <c r="C221">
+        <v>410</v>
+      </c>
+      <c r="D221">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>3.5</v>
+      </c>
+      <c r="B222">
+        <v>0.0574137884595616</v>
+      </c>
+      <c r="C222">
+        <v>494</v>
+      </c>
+      <c r="D222">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>4</v>
+      </c>
+      <c r="B223">
+        <v>0.0586950550908628</v>
+      </c>
+      <c r="C223">
+        <v>690</v>
+      </c>
+      <c r="D223">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>4.5</v>
+      </c>
+      <c r="B224">
+        <v>0.0593765480850442</v>
+      </c>
+      <c r="C224">
+        <v>962</v>
+      </c>
+      <c r="D224">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>5</v>
+      </c>
+      <c r="B225">
+        <v>0.0590212045471525</v>
+      </c>
+      <c r="C225">
+        <v>1098</v>
+      </c>
+      <c r="D225">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>5.5</v>
+      </c>
+      <c r="B226">
+        <v>0.0584877198654761</v>
+      </c>
+      <c r="C226">
+        <v>1406</v>
+      </c>
+      <c r="D226">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>6</v>
+      </c>
+      <c r="B227">
+        <v>0.0580846160385847</v>
+      </c>
+      <c r="C227">
+        <v>1578</v>
+      </c>
+      <c r="D227">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>6.5</v>
+      </c>
+      <c r="B228">
+        <v>0.0578565947246268</v>
+      </c>
+      <c r="C228">
+        <v>2018</v>
+      </c>
+      <c r="D228">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>7</v>
+      </c>
+      <c r="B229">
+        <v>0.057609235599039</v>
+      </c>
+      <c r="C229">
+        <v>2342</v>
+      </c>
+      <c r="D229">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>7.5</v>
+      </c>
+      <c r="B230">
+        <v>0.057383648083802</v>
+      </c>
+      <c r="C230">
+        <v>2634</v>
+      </c>
+      <c r="D230">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>8</v>
+      </c>
+      <c r="B231">
+        <v>0.0570803202866694</v>
+      </c>
+      <c r="C231">
+        <v>2930</v>
+      </c>
+      <c r="D231">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>8.5</v>
+      </c>
+      <c r="B232">
+        <v>0.056786547822857</v>
+      </c>
+      <c r="C232">
+        <v>3402</v>
+      </c>
+      <c r="D232">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>9</v>
+      </c>
+      <c r="B233">
+        <v>0.0565059348993986</v>
+      </c>
+      <c r="C233">
+        <v>3926</v>
+      </c>
+      <c r="D233">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>9.5</v>
+      </c>
+      <c r="B234">
+        <v>0.0562149115811476</v>
+      </c>
+      <c r="C234">
+        <v>4266</v>
+      </c>
+      <c r="D234">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>10</v>
+      </c>
+      <c r="B235">
+        <v>0.0560075223571906</v>
+      </c>
+      <c r="C235">
+        <v>4730</v>
+      </c>
+      <c r="D235">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>10.5</v>
+      </c>
+      <c r="B236">
+        <v>0.0557937317448389</v>
+      </c>
+      <c r="C236">
+        <v>5510</v>
+      </c>
+      <c r="D236">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>11</v>
+      </c>
+      <c r="B237">
+        <v>0.0555903308899957</v>
+      </c>
+      <c r="C237">
+        <v>5562</v>
+      </c>
+      <c r="D237">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>11.5</v>
+      </c>
+      <c r="B238">
+        <v>0.0553645474676409</v>
+      </c>
+      <c r="C238">
+        <v>6410</v>
+      </c>
+      <c r="D238">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>12</v>
+      </c>
+      <c r="B239">
+        <v>0.0551633643938003</v>
+      </c>
+      <c r="C239">
+        <v>6894</v>
+      </c>
+      <c r="D239">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>12.5</v>
+      </c>
+      <c r="B240">
+        <v>0.0549903594604003</v>
+      </c>
+      <c r="C240">
+        <v>7490</v>
+      </c>
+      <c r="D240">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>13</v>
+      </c>
+      <c r="B241">
+        <v>0.0548781692678572</v>
+      </c>
+      <c r="C241">
+        <v>8258</v>
+      </c>
+      <c r="D241">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>13.5</v>
+      </c>
+      <c r="B242">
+        <v>0.0547616181173191</v>
+      </c>
+      <c r="C242">
+        <v>8994</v>
+      </c>
+      <c r="D242">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>14</v>
+      </c>
+      <c r="B243">
+        <v>0.0546464881678898</v>
+      </c>
+      <c r="C243">
+        <v>9446</v>
+      </c>
+      <c r="D243">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>14.5</v>
+      </c>
+      <c r="B244">
+        <v>0.0545147566834536</v>
+      </c>
+      <c r="C244">
+        <v>9978</v>
+      </c>
+      <c r="D244">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>15</v>
+      </c>
+      <c r="B245">
+        <v>0.0543557316209324</v>
+      </c>
+      <c r="C245">
+        <v>11138</v>
+      </c>
+      <c r="D245">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>15.5</v>
+      </c>
+      <c r="B246">
+        <v>0.0542577803396205</v>
+      </c>
+      <c r="C246">
+        <v>11406</v>
+      </c>
+      <c r="D246">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>16</v>
+      </c>
+      <c r="B247">
+        <v>0.0541516592583173</v>
+      </c>
+      <c r="C247">
+        <v>12575</v>
+      </c>
+      <c r="D247">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>16.5</v>
+      </c>
+      <c r="B248">
+        <v>0.0540480453377198</v>
+      </c>
+      <c r="C248">
+        <v>12848</v>
+      </c>
+      <c r="D248">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>17</v>
+      </c>
+      <c r="B249">
+        <v>0.0539328187654663</v>
+      </c>
+      <c r="C249">
+        <v>12060</v>
+      </c>
+      <c r="D249">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>17.5</v>
+      </c>
+      <c r="B250">
+        <v>0.0538617143466165</v>
+      </c>
+      <c r="C250">
+        <v>11804</v>
+      </c>
+      <c r="D250">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>18</v>
+      </c>
+      <c r="B251">
+        <v>0.0537440196794276</v>
+      </c>
+      <c r="C251">
+        <v>11016</v>
+      </c>
+      <c r="D251">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>18.5</v>
+      </c>
+      <c r="B252">
+        <v>0.0535874725056586</v>
+      </c>
+      <c r="C252">
+        <v>10700</v>
+      </c>
+      <c r="D252">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>19</v>
+      </c>
+      <c r="B253">
+        <v>0.0534808927991929</v>
+      </c>
+      <c r="C253">
+        <v>9756</v>
+      </c>
+      <c r="D253">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>19.5</v>
+      </c>
+      <c r="B254">
+        <v>0.0534631037650063</v>
+      </c>
+      <c r="C254">
+        <v>9224</v>
+      </c>
+      <c r="D254">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>20</v>
+      </c>
+      <c r="B255">
+        <v>0.0534962754834844</v>
+      </c>
+      <c r="C255">
+        <v>8408</v>
+      </c>
+      <c r="D255">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>20.5</v>
+      </c>
+      <c r="B256">
+        <v>0.0535586106796387</v>
+      </c>
+      <c r="C256">
+        <v>7452</v>
+      </c>
+      <c r="D256">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>21</v>
+      </c>
+      <c r="B257">
+        <v>0.0536029111255299</v>
+      </c>
+      <c r="C257">
+        <v>7040</v>
+      </c>
+      <c r="D257">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>21.5</v>
+      </c>
+      <c r="B258">
+        <v>0.0535942864172237</v>
+      </c>
+      <c r="C258">
+        <v>5820</v>
+      </c>
+      <c r="D258">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>22</v>
+      </c>
+      <c r="B259">
+        <v>0.0535394637311091</v>
+      </c>
+      <c r="C259">
+        <v>4880</v>
+      </c>
+      <c r="D259">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>22.5</v>
+      </c>
+      <c r="B260">
+        <v>0.0534090084758231</v>
+      </c>
+      <c r="C260">
+        <v>3936</v>
+      </c>
+      <c r="D260">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>23</v>
+      </c>
+      <c r="B261">
+        <v>0.0533262445514065</v>
+      </c>
+      <c r="C261">
+        <v>2999</v>
+      </c>
+      <c r="D261">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>23.5</v>
+      </c>
+      <c r="B262">
+        <v>0.0532452714552573</v>
+      </c>
+      <c r="C262">
+        <v>2180</v>
+      </c>
+      <c r="D262">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>24</v>
+      </c>
+      <c r="B263">
+        <v>0.0531746946735147</v>
+      </c>
+      <c r="C263">
+        <v>1620</v>
+      </c>
+      <c r="D263">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>24.5</v>
+      </c>
+      <c r="B264">
+        <v>0.0531121184494322</v>
+      </c>
+      <c r="C264">
+        <v>1208</v>
+      </c>
+      <c r="D264">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>25</v>
+      </c>
+      <c r="B265">
+        <v>0.0532023597927863</v>
+      </c>
+      <c r="C265">
+        <v>942</v>
+      </c>
+      <c r="D265">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>25.5</v>
+      </c>
+      <c r="B266">
+        <v>0.0534285976462168</v>
+      </c>
+      <c r="C266">
+        <v>584</v>
+      </c>
+      <c r="D266">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>26</v>
+      </c>
+      <c r="B267">
+        <v>0.0536700503926882</v>
+      </c>
+      <c r="C267">
+        <v>284</v>
+      </c>
+      <c r="D267">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>26.5</v>
+      </c>
+      <c r="B268">
+        <v>0.0537826617558797</v>
+      </c>
+      <c r="C268">
+        <v>192</v>
+      </c>
+      <c r="D268">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>27</v>
+      </c>
+      <c r="B269">
+        <v>0.0539398193359375</v>
+      </c>
+      <c r="C269">
+        <v>104</v>
+      </c>
+      <c r="D269">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>27.5</v>
+      </c>
+      <c r="B270">
+        <v>0.0537341435750326</v>
+      </c>
+      <c r="C270">
+        <v>24</v>
+      </c>
+      <c r="D270">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>28</v>
+      </c>
+      <c r="B271">
+        <v>0.0533447265625</v>
+      </c>
+      <c r="C271">
+        <v>1</v>
+      </c>
+      <c r="D271">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>0</v>
+      </c>
+      <c r="B273">
+        <v>0.233562469482422</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>0.5</v>
+      </c>
+      <c r="B274">
+        <v>0.154685974121094</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>1</v>
+      </c>
+      <c r="B275">
+        <v>0.106765747070312</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>1.5</v>
+      </c>
+      <c r="B276">
+        <v>0.0774078369140625</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>2</v>
+      </c>
+      <c r="B277">
+        <v>0.0647201538085938</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>2.5</v>
+      </c>
+      <c r="B278">
+        <v>0.0567741394042969</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>3</v>
+      </c>
+      <c r="B279">
+        <v>0.0579910278320312</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>3.5</v>
+      </c>
+      <c r="B280">
+        <v>0.0578575134277344</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>4</v>
+      </c>
+      <c r="B281">
+        <v>0.05987548828125</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>4.5</v>
+      </c>
+      <c r="B282">
+        <v>0.0594558715820312</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>5</v>
+      </c>
+      <c r="B283">
+        <v>0.0582656860351562</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>5.5</v>
+      </c>
+      <c r="B284">
+        <v>0.0572471618652344</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>6</v>
+      </c>
+      <c r="B285">
+        <v>0.0570640563964844</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>6.5</v>
+      </c>
+      <c r="B286">
+        <v>0.0573654174804688</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>7</v>
+      </c>
+      <c r="B287">
+        <v>0.0579109191894531</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>7.5</v>
+      </c>
+      <c r="B288">
+        <v>0.0577468872070312</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>8</v>
+      </c>
+      <c r="B289">
+        <v>0.0572509765625</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>8.5</v>
+      </c>
+      <c r="B290">
+        <v>0.0569839477539062</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>9</v>
+      </c>
+      <c r="B291">
+        <v>0.0569725036621094</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>9.5</v>
+      </c>
+      <c r="B292">
+        <v>0.0569000244140625</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>10</v>
+      </c>
+      <c r="B293">
+        <v>0.0567283630371094</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>10.5</v>
+      </c>
+      <c r="B294">
+        <v>0.0559768676757812</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>11</v>
+      </c>
+      <c r="B295">
+        <v>0.0556488037109375</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>11.5</v>
+      </c>
+      <c r="B296">
+        <v>0.0559196472167969</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>12</v>
+      </c>
+      <c r="B297">
+        <v>0.0557441711425781</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>12.5</v>
+      </c>
+      <c r="B298">
+        <v>0.0554885864257812</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>13</v>
+      </c>
+      <c r="B299">
+        <v>0.0552101135253906</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>13.5</v>
+      </c>
+      <c r="B300">
+        <v>0.0558013916015625</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>14</v>
+      </c>
+      <c r="B301">
+        <v>0.0568466186523438</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>14.5</v>
+      </c>
+      <c r="B302">
+        <v>0.0569267272949219</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>15</v>
+      </c>
+      <c r="B303">
+        <v>0.0565986633300781</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>15.5</v>
+      </c>
+      <c r="B304">
+        <v>0.0561676025390625</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>16</v>
+      </c>
+      <c r="B305">
+        <v>0.0560760498046875</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>0</v>
+      </c>
+      <c r="B307">
+        <v>0.233562469482422</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>0.5</v>
+      </c>
+      <c r="B308">
+        <v>0.155246734619141</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>1</v>
+      </c>
+      <c r="B309">
+        <v>0.107898712158203</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>1.5</v>
+      </c>
+      <c r="B310">
+        <v>0.0785713195800781</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>2</v>
+      </c>
+      <c r="B311">
+        <v>0.0654411315917969</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>2.5</v>
+      </c>
+      <c r="B312">
+        <v>0.057525634765625</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>3</v>
+      </c>
+      <c r="B313">
+        <v>0.0592536926269531</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>3.5</v>
+      </c>
+      <c r="B314">
+        <v>0.0592765808105469</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>4</v>
+      </c>
+      <c r="B315">
+        <v>0.0606956481933594</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>4.5</v>
+      </c>
+      <c r="B316">
+        <v>0.0598373413085938</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>5</v>
+      </c>
+      <c r="B317">
+        <v>0.0587959289550781</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>5.5</v>
+      </c>
+      <c r="B318">
+        <v>0.0584983825683594</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>6</v>
+      </c>
+      <c r="B319">
+        <v>0.0585365295410156</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>6.5</v>
+      </c>
+      <c r="B320">
+        <v>0.058197021484375</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>7</v>
+      </c>
+      <c r="B321">
+        <v>0.0576286315917969</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>7.5</v>
+      </c>
+      <c r="B322">
+        <v>0.0571670532226562</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>8</v>
+      </c>
+      <c r="B323">
+        <v>0.0567855834960938</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>8.5</v>
+      </c>
+      <c r="B324">
+        <v>0.0572700500488281</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>9</v>
+      </c>
+      <c r="B325">
+        <v>0.0581283569335938</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>9.5</v>
+      </c>
+      <c r="B326">
+        <v>0.0592422485351562</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>10</v>
+      </c>
+      <c r="B327">
+        <v>0.0590324401855469</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>10.5</v>
+      </c>
+      <c r="B328">
+        <v>0.0583534240722656</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>11</v>
+      </c>
+      <c r="B329">
+        <v>0.0580329895019531</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>11.5</v>
+      </c>
+      <c r="B330">
+        <v>0.057891845703125</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>12</v>
+      </c>
+      <c r="B331">
+        <v>0.0576400756835938</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>12.5</v>
+      </c>
+      <c r="B332">
+        <v>0.0573196411132812</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>13</v>
+      </c>
+      <c r="B333">
+        <v>0.0574531555175781</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>13.5</v>
+      </c>
+      <c r="B334">
+        <v>0.0571212768554688</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>14</v>
+      </c>
+      <c r="B335">
+        <v>0.0573692321777344</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>14.5</v>
+      </c>
+      <c r="B336">
+        <v>0.057159423828125</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>15</v>
+      </c>
+      <c r="B337">
+        <v>0.0574951171875</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>15.5</v>
+      </c>
+      <c r="B338">
+        <v>0.0576629638671875</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>16</v>
+      </c>
+      <c r="B339">
+        <v>0.0580520629882812</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>0</v>
+      </c>
+      <c r="B341">
+        <v>0.233562469482422</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>0.5</v>
+      </c>
+      <c r="B342">
+        <v>0.155464172363281</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>1</v>
+      </c>
+      <c r="B343">
+        <v>0.107288360595703</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>1.5</v>
+      </c>
+      <c r="B344">
+        <v>0.0775604248046875</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>2</v>
+      </c>
+      <c r="B345">
+        <v>0.0638504028320312</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>2.5</v>
+      </c>
+      <c r="B346">
+        <v>0.0554122924804688</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>3</v>
+      </c>
+      <c r="B347">
+        <v>0.0564918518066406</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <v>3.5</v>
+      </c>
+      <c r="B348">
+        <v>0.0566329956054688</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>4</v>
+      </c>
+      <c r="B349">
+        <v>0.059906005859375</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>4.5</v>
+      </c>
+      <c r="B350">
+        <v>0.0599365234375</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>5</v>
+      </c>
+      <c r="B351">
+        <v>0.0598831176757812</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>5.5</v>
+      </c>
+      <c r="B352">
+        <v>0.0595626831054688</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>6</v>
+      </c>
+      <c r="B353">
+        <v>0.0592155456542969</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>6.5</v>
+      </c>
+      <c r="B354">
+        <v>0.0589447021484375</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>7</v>
+      </c>
+      <c r="B355">
+        <v>0.0586624145507812</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>7.5</v>
+      </c>
+      <c r="B356">
+        <v>0.0582313537597656</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>8</v>
+      </c>
+      <c r="B357">
+        <v>0.0574378967285156</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <v>8.5</v>
+      </c>
+      <c r="B358">
+        <v>0.0576057434082031</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>9</v>
+      </c>
+      <c r="B359">
+        <v>0.0576515197753906</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>9.5</v>
+      </c>
+      <c r="B360">
+        <v>0.0576896667480469</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <v>10</v>
+      </c>
+      <c r="B361">
+        <v>0.0568580627441406</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>10.5</v>
+      </c>
+      <c r="B362">
+        <v>0.0559616088867187</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>11</v>
+      </c>
+      <c r="B363">
+        <v>0.0548782348632812</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>11.5</v>
+      </c>
+      <c r="B364">
+        <v>0.0536956787109375</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <v>12</v>
+      </c>
+      <c r="B365">
+        <v>0.0533294677734375</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366">
+        <v>12.5</v>
+      </c>
+      <c r="B366">
+        <v>0.0537452697753906</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367">
+        <v>13</v>
+      </c>
+      <c r="B367">
+        <v>0.0545768737792969</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368">
+        <v>13.5</v>
+      </c>
+      <c r="B368">
+        <v>0.0543441772460938</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369">
+        <v>14</v>
+      </c>
+      <c r="B369">
+        <v>0.0539169311523438</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370">
+        <v>14.5</v>
+      </c>
+      <c r="B370">
+        <v>0.0534744262695312</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371">
+        <v>15</v>
+      </c>
+      <c r="B371">
+        <v>0.0524177551269531</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372">
+        <v>15.5</v>
+      </c>
+      <c r="B372">
+        <v>0.0521926879882812</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373">
+        <v>16</v>
+      </c>
+      <c r="B373">
+        <v>0.0518646240234375</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>